--- a/laporan Buku Tamu.xlsx
+++ b/laporan Buku Tamu.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
   <si>
     <t>No</t>
   </si>
@@ -90,6 +90,21 @@
   </si>
   <si>
     <t>diffa</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>tuya</t>
+  </si>
+  <si>
+    <t>btn</t>
+  </si>
+  <si>
+    <t>sasad</t>
+  </si>
+  <si>
+    <t>layangan</t>
   </si>
 </sst>
 </file>
@@ -429,7 +444,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -545,6 +560,29 @@
       </c>
       <c r="G5" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>142131</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/laporan Buku Tamu.xlsx
+++ b/laporan Buku Tamu.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>No</t>
   </si>
@@ -86,25 +86,19 @@
     <t>mabar</t>
   </si>
   <si>
-    <t>bayu</t>
-  </si>
-  <si>
-    <t>diffa</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>tuya</t>
-  </si>
-  <si>
-    <t>btn</t>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>bayu kunem</t>
+  </si>
+  <si>
+    <t>kebon</t>
   </si>
   <si>
     <t>sasad</t>
   </si>
   <si>
-    <t>layangan</t>
+    <t>bakuhantam</t>
   </si>
 </sst>
 </file>
@@ -444,7 +438,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -544,45 +538,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>123912</v>
+        <v>8765646</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
         <v>27</v>
-      </c>
-      <c r="E6">
-        <v>142131</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/laporan Buku Tamu.xlsx
+++ b/laporan Buku Tamu.xlsx
@@ -15,27 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>TANGGAL</t>
-  </si>
-  <si>
-    <t>NAMA_TAMU</t>
-  </si>
-  <si>
-    <t>ALAMAT</t>
-  </si>
-  <si>
-    <t>NO TELEPON/HP</t>
-  </si>
-  <si>
-    <t>BERTEMU DENGAN</t>
-  </si>
-  <si>
-    <t>KEPENTINGAN</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+  <si>
+    <t>Laporan Buku Tamu</t>
   </si>
   <si>
     <t>2026-09-21</t>
@@ -72,18 +54,6 @@
   </si>
   <si>
     <t>meeting</t>
-  </si>
-  <si>
-    <t>fajar</t>
-  </si>
-  <si>
-    <t>gebrong</t>
-  </si>
-  <si>
-    <t>kelvin</t>
-  </si>
-  <si>
-    <t>mabar</t>
   </si>
   <si>
     <t>2026-09-25</t>
@@ -106,13 +76,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -137,8 +116,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,30 +420,12 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" customHeight="1" ht="22">
+      <c r="A1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -469,22 +433,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -492,22 +456,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -518,45 +482,25 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>12930129</v>
+        <v>8765646</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
-        <v>8765646</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
